--- a/output/pdf_financials_xlsx/ROOF.xlsx
+++ b/output/pdf_financials_xlsx/ROOF.xlsx
@@ -2751,22 +2751,22 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.5438539999999999</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.571477</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.53433</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.539108</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.32509</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.396911</v>
       </c>
     </row>
     <row r="93">
@@ -5170,7 +5170,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -6364,7 +6368,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -7838,7 +7846,11 @@
           <t>Reserves (Note 14)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -8702,7 +8714,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -9080,7 +9096,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="n">
         <v>0.5438539999999999</v>
       </c>

--- a/output/pdf_financials_xlsx/ROOF.xlsx
+++ b/output/pdf_financials_xlsx/ROOF.xlsx
@@ -708,19 +708,19 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.019703</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.010402</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.003358</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.049473</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         <v>-6.596793</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-7.207912</v>
+        <v>-7.229912</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-8.445257</v>
+        <v>-8.46496</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.933703</v>
+        <v>-6.944105</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-9.822925</v>
+        <v>-9.826283</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-14.751864</v>
+        <v>-14.801337</v>
       </c>
     </row>
     <row r="28">
@@ -1157,19 +1157,19 @@
         <v>-6.27317</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.745946</v>
+        <v>-6.767946</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.369258</v>
+        <v>-7.388961</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.81342</v>
+        <v>-5.823822</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-8.531077</v>
+        <v>-8.534435</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-13.453649</v>
+        <v>-13.503122</v>
       </c>
     </row>
     <row r="30">
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-2816.033714396435</v>
+        <v>-2821.072466576245</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-1331.796730719095</v>
+        <v>-1332.320952153476</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-2266.503758511825</v>
+        <v>-2274.838355352047</v>
       </c>
     </row>
     <row r="31">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.977795</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.948876</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.114166</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>7.648311</v>
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.977795</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.948876</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.114166</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>7.648311</v>
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.04268</v>
+        <v>0.064885</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.415454</v>
+        <v>0.466578</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.278343</v>
+        <v>0.164177</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.249639</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">

--- a/output/pdf_financials_xlsx/ROOF.xlsx
+++ b/output/pdf_financials_xlsx/ROOF.xlsx
@@ -3439,16 +3439,16 @@
         <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>2.652533</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>3.267817</v>
       </c>
     </row>
     <row r="121">
@@ -10154,7 +10154,11 @@
           <t>Issuance of common shares, net of issuance costs 12</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -11856,7 +11860,11 @@
           <t>Issuance of common shares, net of issuance costs 11</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -13538,7 +13546,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs (Note 12)</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ROOF.xlsx
+++ b/output/pdf_financials_xlsx/ROOF.xlsx
@@ -836,13 +836,13 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.244321</v>
+        <v>-0.123962</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.261776</v>
+        <v>-0.206758</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.490105</v>
+        <v>-0.490105</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>5.419044</v>
@@ -1216,10 +1216,10 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-2.892996625206314</v>
+        <v>-1.467829812639213</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-3.775414089700698</v>
+        <v>-2.981927550112833</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-4.989399796903672</v>
@@ -2964,10 +2964,10 @@
         <v>-0.164063</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.032384</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>-0.021315</v>
+        <v>0.081081</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0</v>
@@ -3089,7 +3089,7 @@
         <v>-0.160037</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.538897</v>
+        <v>0.571281</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.182831</v>
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -3339,16 +3339,16 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.026036</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.016782</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.061499</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.026584</v>
       </c>
     </row>
     <row r="117">
@@ -9832,7 +9832,11 @@
           <t>Acquisition of intangible assets 8</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -11630,7 +11634,11 @@
           <t>Acquisition of intangible assets 7</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -13054,7 +13062,11 @@
           <t>GST Receivables</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -13322,7 +13334,11 @@
           <t>Acquisition of intangible assets (Note 8)</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -14464,7 +14480,11 @@
           <t>Acquisition of intangible assets (Note 7)</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -14556,7 +14576,11 @@
           <t>Proceeds on disposition of property, plant and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -15334,7 +15358,11 @@
           <t>Proceeds on disposition of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -16790,7 +16818,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -18540,7 +18572,11 @@
           <t>Income tax recovery 20</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -20728,7 +20764,11 @@
           <t>Income tax recovery (Notes 10 and 19)</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
@@ -22162,7 +22202,11 @@
           <t>Income tax recovery (Note 9 and 16)</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
